--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>848099</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>830000</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>810542</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>803030</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>801450</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>797735</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>793390</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>779636</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>771249.5</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>750000</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>725000</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>700582.5</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>682500</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>677609</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>674433</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>668150</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>667062.5</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>662500</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>650000</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>644587.5</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>627500</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>621530</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>615060</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>606944</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>600810</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>600000</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>600000</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>585000</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>583510</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>557101.5</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>544395</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>530430</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -811,9 +710,6 @@
       </c>
       <c r="B34">
         <v>511886.5</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>848099</v>
       </c>
+      <c r="C2">
+        <v>754440</v>
+      </c>
+      <c r="D2">
+        <v>93659</v>
+      </c>
+      <c r="E2">
+        <v>12.41437357510207</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>830000</v>
       </c>
+      <c r="C3">
+        <v>733396</v>
+      </c>
+      <c r="D3">
+        <v>96604</v>
+      </c>
+      <c r="E3">
+        <v>13.172147107429</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>810542</v>
       </c>
+      <c r="C4">
+        <v>720830</v>
+      </c>
+      <c r="D4">
+        <v>89712</v>
+      </c>
+      <c r="E4">
+        <v>12.44565292787481</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>803030</v>
       </c>
+      <c r="C5">
+        <v>740660</v>
+      </c>
+      <c r="D5">
+        <v>62370</v>
+      </c>
+      <c r="E5">
+        <v>8.420867874598326</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>801450</v>
       </c>
+      <c r="C6">
+        <v>710390</v>
+      </c>
+      <c r="D6">
+        <v>91060</v>
+      </c>
+      <c r="E6">
+        <v>12.81831106856797</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>797735</v>
       </c>
+      <c r="C7">
+        <v>694086</v>
+      </c>
+      <c r="D7">
+        <v>103649</v>
+      </c>
+      <c r="E7">
+        <v>14.9331639018796</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>793390</v>
       </c>
+      <c r="C8">
+        <v>710612.5</v>
+      </c>
+      <c r="D8">
+        <v>82777.5</v>
+      </c>
+      <c r="E8">
+        <v>11.64875371598444</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>779636</v>
       </c>
+      <c r="C9">
+        <v>682337.5</v>
+      </c>
+      <c r="D9">
+        <v>97298.5</v>
+      </c>
+      <c r="E9">
+        <v>14.25958561562277</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>771249.5</v>
       </c>
+      <c r="C10">
+        <v>689726</v>
+      </c>
+      <c r="D10">
+        <v>81523.5</v>
+      </c>
+      <c r="E10">
+        <v>11.81969361746549</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,235 +562,470 @@
       <c r="B11">
         <v>750000</v>
       </c>
+      <c r="C11">
+        <v>662383</v>
+      </c>
+      <c r="D11">
+        <v>87617</v>
+      </c>
+      <c r="E11">
+        <v>13.22754358128153</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12">
-        <v>725000</v>
+        <v>730000</v>
+      </c>
+      <c r="C12">
+        <v>643710</v>
+      </c>
+      <c r="D12">
+        <v>86290</v>
+      </c>
+      <c r="E12">
+        <v>13.40510478320982</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="B13">
-        <v>700582.5</v>
+        <v>725000</v>
+      </c>
+      <c r="C13">
+        <v>642950</v>
+      </c>
+      <c r="D13">
+        <v>82050</v>
+      </c>
+      <c r="E13">
+        <v>12.761490006999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B14">
-        <v>682500</v>
+        <v>700582.5</v>
+      </c>
+      <c r="C14">
+        <v>620610</v>
+      </c>
+      <c r="D14">
+        <v>79972.5</v>
+      </c>
+      <c r="E14">
+        <v>12.88611205104655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="B15">
-        <v>677609</v>
+        <v>682500</v>
+      </c>
+      <c r="C15">
+        <v>612188</v>
+      </c>
+      <c r="D15">
+        <v>70312</v>
+      </c>
+      <c r="E15">
+        <v>11.48536070618828</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="B16">
-        <v>674433</v>
+        <v>677609</v>
+      </c>
+      <c r="C16">
+        <v>595509.5</v>
+      </c>
+      <c r="D16">
+        <v>82099.5</v>
+      </c>
+      <c r="E16">
+        <v>13.78642993940482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="B17">
-        <v>668150</v>
+        <v>674433</v>
+      </c>
+      <c r="C17">
+        <v>600153</v>
+      </c>
+      <c r="D17">
+        <v>74280</v>
+      </c>
+      <c r="E17">
+        <v>12.37684390480427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="B18">
-        <v>667062.5</v>
+        <v>668150</v>
+      </c>
+      <c r="C18">
+        <v>600000</v>
+      </c>
+      <c r="D18">
+        <v>68150</v>
+      </c>
+      <c r="E18">
+        <v>11.35833333333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="B19">
-        <v>662500</v>
+        <v>667062.5</v>
+      </c>
+      <c r="C19">
+        <v>575180</v>
+      </c>
+      <c r="D19">
+        <v>91882.5</v>
+      </c>
+      <c r="E19">
+        <v>15.97456448416148</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="B20">
-        <v>650000</v>
+        <v>662500</v>
+      </c>
+      <c r="C20">
+        <v>580917</v>
+      </c>
+      <c r="D20">
+        <v>81583</v>
+      </c>
+      <c r="E20">
+        <v>14.0438307021485</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="B21">
-        <v>644587.5</v>
+        <v>650000</v>
+      </c>
+      <c r="C21">
+        <v>581028</v>
+      </c>
+      <c r="D21">
+        <v>68972</v>
+      </c>
+      <c r="E21">
+        <v>11.87068437321437</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="B22">
-        <v>627500</v>
+        <v>644587.5</v>
+      </c>
+      <c r="C22">
+        <v>564293</v>
+      </c>
+      <c r="D22">
+        <v>80294.5</v>
+      </c>
+      <c r="E22">
+        <v>14.22922134423075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="B23">
-        <v>621530</v>
+        <v>627500</v>
+      </c>
+      <c r="C23">
+        <v>566897.5</v>
+      </c>
+      <c r="D23">
+        <v>60602.5</v>
+      </c>
+      <c r="E23">
+        <v>10.69020413743225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="B24">
-        <v>615060</v>
+        <v>621530</v>
+      </c>
+      <c r="C24">
+        <v>537500</v>
+      </c>
+      <c r="D24">
+        <v>84030</v>
+      </c>
+      <c r="E24">
+        <v>15.63348837209302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B25">
-        <v>606944</v>
+        <v>615060</v>
+      </c>
+      <c r="C25">
+        <v>539803</v>
+      </c>
+      <c r="D25">
+        <v>75257</v>
+      </c>
+      <c r="E25">
+        <v>13.94156757187344</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="B26">
-        <v>600810</v>
+        <v>606944</v>
+      </c>
+      <c r="C26">
+        <v>543420</v>
+      </c>
+      <c r="D26">
+        <v>63524</v>
+      </c>
+      <c r="E26">
+        <v>11.689669132531</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="B27">
-        <v>600000</v>
+        <v>600810</v>
+      </c>
+      <c r="C27">
+        <v>511484</v>
+      </c>
+      <c r="D27">
+        <v>89326</v>
+      </c>
+      <c r="E27">
+        <v>17.46408489806133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="B28">
         <v>600000</v>
       </c>
+      <c r="C28">
+        <v>531576</v>
+      </c>
+      <c r="D28">
+        <v>68424</v>
+      </c>
+      <c r="E28">
+        <v>12.87191295318073</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="B29">
-        <v>585000</v>
+        <v>600000</v>
+      </c>
+      <c r="C29">
+        <v>520043</v>
+      </c>
+      <c r="D29">
+        <v>79957</v>
+      </c>
+      <c r="E29">
+        <v>15.37507475343385</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="B30">
-        <v>583510</v>
+        <v>585000</v>
+      </c>
+      <c r="C30">
+        <v>552810</v>
+      </c>
+      <c r="D30">
+        <v>32190</v>
+      </c>
+      <c r="E30">
+        <v>5.822977153090569</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="B31">
-        <v>557101.5</v>
+        <v>583510</v>
+      </c>
+      <c r="C31">
+        <v>534375</v>
+      </c>
+      <c r="D31">
+        <v>49135</v>
+      </c>
+      <c r="E31">
+        <v>9.1948538011696</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="B32">
-        <v>544395</v>
+        <v>557101.5</v>
+      </c>
+      <c r="C32">
+        <v>479064</v>
+      </c>
+      <c r="D32">
+        <v>78037.5</v>
+      </c>
+      <c r="E32">
+        <v>16.28957717549222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="B33">
-        <v>530430</v>
+        <v>544395</v>
+      </c>
+      <c r="C33">
+        <v>491900</v>
+      </c>
+      <c r="D33">
+        <v>52495</v>
+      </c>
+      <c r="E33">
+        <v>10.67188452937589</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Contulmo</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>530430</v>
+      </c>
+      <c r="C34">
+        <v>483620</v>
+      </c>
+      <c r="D34">
+        <v>46810</v>
+      </c>
+      <c r="E34">
+        <v>9.679086886398402</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Tirúa</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>511886.5</v>
+      </c>
+      <c r="C35">
+        <v>500000</v>
+      </c>
+      <c r="D35">
+        <v>11886.5</v>
+      </c>
+      <c r="E35">
+        <v>2.377300000000004</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +1203,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="B17">
@@ -897,7 +1213,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B18">

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_biobio.xlsx
@@ -1035,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1044,290 +1044,201 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>557101.5</v>
+          <t>Cañete</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Antuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>803030</v>
+          <t>Contulmo</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arauco</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>793390</v>
+          <t>Curanilahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cabrero</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>668150</v>
+          <t>Lebu</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cañete</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>583510</v>
+          <t>Los Alamos</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>797735</v>
+          <t>Laja</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>830000</v>
+          <t>Los Angeles</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Contulmo</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>530430</v>
+          <t>Mulchén</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coronel</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>725000</v>
+          <t>Nacimiento</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>606944</v>
+          <t>Negrete</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>615060</v>
+          <t>Quilaco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualpén</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>750000</v>
+          <t>Quilleco</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hualqui</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>644587.5</v>
+          <t>San Rosendo</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Laja</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>810542</v>
+          <t>Tucapel</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lebu</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>544395</v>
+          <t>Chiguayante</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>585000</v>
+          <t>Concepción</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>700582.5</v>
+          <t>Coronel</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lota</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>600000</v>
+          <t>Florida</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mulchén</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>621530</v>
+          <t>Hualqui</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>771249.5</v>
+          <t>Lota</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Negrete</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>667062.5</v>
+          <t>San Pedro de la Paz</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Penco</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>677609</v>
+          <t>Santa Juana</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quilaco</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>600810</v>
+          <t>Yumbel</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quilleco</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>650000</v>
+          <t>Cabrero</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>848099</v>
+          <t>Antuco</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>801450</v>
+          <t>Alto Biobío</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>600000</v>
+          <t>Tirúa</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>662500</v>
+          <t>Hualpén</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1336,18 +1247,12 @@
           <t>Talcahuano</t>
         </is>
       </c>
-      <c r="B30">
-        <v>779636</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tirúa</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>511886.5</v>
+          <t>Penco</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1356,28 +1261,19 @@
           <t>Tomé</t>
         </is>
       </c>
-      <c r="B32">
-        <v>674433</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tucapel</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>682500</v>
+          <t>Arauco</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yumbel</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>627500</v>
+          <t>Santa Bárbara</t>
+        </is>
       </c>
     </row>
   </sheetData>
